--- a/panchang-data/Winnipeg_Manitoba2026.xlsx
+++ b/panchang-data/Winnipeg_Manitoba2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5425">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16300,6 +16300,9 @@
   </si>
   <si>
     <t>121°03'19.91</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16789,7 +16792,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16875,7 +16878,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>53</v>
@@ -16961,7 +16964,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>73</v>
@@ -17047,7 +17050,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
@@ -17133,7 +17136,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>109</v>
@@ -17219,7 +17222,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>127</v>
@@ -17305,7 +17308,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>145</v>
@@ -17391,7 +17394,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17477,7 +17480,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>53</v>
@@ -17563,7 +17566,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>73</v>
@@ -17649,7 +17652,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>92</v>
@@ -17735,7 +17738,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>109</v>
@@ -17821,7 +17824,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>127</v>
@@ -17907,7 +17910,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>145</v>
@@ -17993,7 +17996,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18079,7 +18082,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>53</v>
@@ -18165,7 +18168,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>73</v>
@@ -18251,7 +18254,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>92</v>
@@ -18337,7 +18340,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>109</v>
@@ -18423,7 +18426,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>127</v>
@@ -18509,7 +18512,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>145</v>
@@ -18595,7 +18598,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18681,7 +18684,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>53</v>
@@ -18767,7 +18770,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>73</v>
@@ -18853,7 +18856,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>92</v>
@@ -18939,7 +18942,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>109</v>
@@ -19025,7 +19028,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>127</v>
@@ -19111,7 +19114,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>145</v>
@@ -19197,7 +19200,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19283,7 +19286,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>53</v>
@@ -19369,7 +19372,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>73</v>
@@ -19455,7 +19458,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>92</v>
@@ -19541,7 +19544,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>109</v>
@@ -19627,7 +19630,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>127</v>
@@ -19713,7 +19716,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>145</v>
@@ -19799,7 +19802,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19885,7 +19888,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>53</v>
@@ -19971,7 +19974,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>73</v>
@@ -20057,7 +20060,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>92</v>
@@ -20143,7 +20146,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>109</v>
@@ -20229,7 +20232,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>127</v>
@@ -20315,7 +20318,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>145</v>
@@ -20401,7 +20404,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20487,7 +20490,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>53</v>
@@ -20573,7 +20576,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>73</v>
@@ -20659,7 +20662,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>92</v>
@@ -20745,7 +20748,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>109</v>
@@ -20831,7 +20834,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>127</v>
@@ -20917,7 +20920,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>145</v>
@@ -21003,7 +21006,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21089,7 +21092,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>53</v>
@@ -21175,7 +21178,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>73</v>
@@ -21261,7 +21264,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>92</v>
@@ -21347,7 +21350,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>109</v>
@@ -21433,7 +21436,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>127</v>
@@ -21519,7 +21522,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>145</v>
@@ -21605,7 +21608,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21691,7 +21694,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>53</v>
@@ -21777,7 +21780,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>73</v>
@@ -21863,7 +21866,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>92</v>
@@ -21949,7 +21952,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>571</v>
+        <v>1000</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>109</v>
@@ -22035,7 +22038,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>127</v>
@@ -22121,7 +22124,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>145</v>
@@ -22207,7 +22210,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22293,7 +22296,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>53</v>
@@ -22379,7 +22382,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>73</v>
@@ -22465,7 +22468,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>92</v>
@@ -22551,7 +22554,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>109</v>
@@ -22637,7 +22640,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>127</v>
@@ -22723,7 +22726,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>145</v>
@@ -22809,7 +22812,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22895,7 +22898,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>53</v>
@@ -22981,7 +22984,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>73</v>
@@ -23067,7 +23070,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>92</v>
@@ -23153,7 +23156,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>109</v>
@@ -23239,7 +23242,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>127</v>
@@ -23325,7 +23328,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>145</v>
@@ -23411,7 +23414,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23497,7 +23500,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>53</v>
@@ -23583,7 +23586,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>73</v>
@@ -23669,7 +23672,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>92</v>
@@ -23755,7 +23758,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>109</v>
@@ -23841,7 +23844,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>127</v>
@@ -23927,7 +23930,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>145</v>
@@ -24013,7 +24016,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24099,7 +24102,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>53</v>
@@ -24185,7 +24188,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>73</v>
@@ -24271,7 +24274,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>92</v>
@@ -24357,7 +24360,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>109</v>
@@ -24443,7 +24446,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>127</v>
@@ -24529,7 +24532,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1000</v>
+        <v>1441</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>145</v>
@@ -24615,7 +24618,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24701,7 +24704,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>53</v>
@@ -24787,7 +24790,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>73</v>
@@ -24873,7 +24876,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>92</v>
@@ -24959,7 +24962,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>109</v>
@@ -25045,7 +25048,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>127</v>
@@ -25131,7 +25134,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>145</v>
@@ -25217,7 +25220,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25303,7 +25306,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>53</v>
@@ -25389,7 +25392,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>73</v>
@@ -25475,7 +25478,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>92</v>
@@ -25561,7 +25564,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>109</v>
@@ -25647,7 +25650,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>127</v>
@@ -25733,7 +25736,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>145</v>
@@ -25819,7 +25822,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25905,7 +25908,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>53</v>
@@ -25991,7 +25994,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>73</v>
@@ -26077,7 +26080,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>92</v>
@@ -26163,7 +26166,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>109</v>
@@ -26249,7 +26252,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>127</v>
@@ -26335,7 +26338,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>145</v>
@@ -26421,7 +26424,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26507,7 +26510,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>53</v>
@@ -26593,7 +26596,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>73</v>
@@ -26679,7 +26682,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>92</v>
@@ -26765,7 +26768,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>109</v>
@@ -26851,7 +26854,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>127</v>
@@ -26937,7 +26940,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>145</v>
@@ -27023,7 +27026,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27109,7 +27112,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1441</v>
+        <v>1879</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>53</v>
@@ -27195,7 +27198,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>73</v>
@@ -27281,7 +27284,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>92</v>
@@ -27367,7 +27370,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>109</v>
@@ -27453,7 +27456,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>127</v>
@@ -27539,7 +27542,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>145</v>
@@ -27625,7 +27628,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27711,7 +27714,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>53</v>
@@ -27797,7 +27800,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>73</v>
@@ -27883,7 +27886,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>92</v>
@@ -27969,7 +27972,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>109</v>
@@ -28055,7 +28058,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>127</v>
@@ -28141,7 +28144,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>145</v>
@@ -28227,7 +28230,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28313,7 +28316,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>53</v>
@@ -28399,7 +28402,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1879</v>
+        <v>2300</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>73</v>
@@ -28485,7 +28488,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>92</v>
@@ -28571,7 +28574,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>109</v>
@@ -28657,7 +28660,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>127</v>
@@ -28743,7 +28746,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>145</v>
@@ -28829,7 +28832,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28915,7 +28918,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>53</v>
@@ -29001,7 +29004,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>73</v>
@@ -29087,7 +29090,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>92</v>
@@ -29173,7 +29176,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>109</v>
@@ -29259,7 +29262,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>127</v>
@@ -29345,7 +29348,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>145</v>
@@ -29431,7 +29434,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29517,7 +29520,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>53</v>
@@ -29603,7 +29606,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1879</v>
+        <v>5424</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>73</v>
@@ -29689,7 +29692,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>92</v>
@@ -29775,7 +29778,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>109</v>
@@ -29861,7 +29864,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>127</v>
@@ -29947,7 +29950,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>145</v>
@@ -30033,7 +30036,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30119,7 +30122,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>53</v>
@@ -30205,7 +30208,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>73</v>
@@ -30291,7 +30294,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>92</v>
@@ -30377,7 +30380,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>109</v>
@@ -30463,7 +30466,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>127</v>
@@ -30549,7 +30552,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>145</v>
@@ -30635,7 +30638,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30721,7 +30724,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>53</v>
@@ -30807,7 +30810,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>73</v>
@@ -30893,7 +30896,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2300</v>
+        <v>5424</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>92</v>
